--- a/data/sce_compartment_curation/mitochondrial_intermembrane_space_annotations_manual_v2.xlsx
+++ b/data/sce_compartment_curation/mitochondrial_intermembrane_space_annotations_manual_v2.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>YKL137W</t>
+          <t>YBL107C</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>YPL132W</t>
+          <t>YIL156W-B</t>
         </is>
       </c>
     </row>
@@ -461,7 +461,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>YLR043C</t>
+          <t>YKL152C</t>
         </is>
       </c>
     </row>
@@ -471,7 +471,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>YIR037W</t>
+          <t>YKL087C</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>YGR181W</t>
+          <t>YMR002W</t>
         </is>
       </c>
     </row>
@@ -491,7 +491,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>YDR226W</t>
+          <t>YLR038C</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>YCR079W</t>
+          <t>YJL066C</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>YIL156W-B</t>
+          <t>YKL137W</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>YLR218C</t>
+          <t>YOR211C</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>YKR071C</t>
+          <t>YLR193C</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>YEL039C</t>
+          <t>YDR487C</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>YKL150W</t>
+          <t>YKL067W</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>YDR185C</t>
+          <t>YJR034W</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>YBR056W</t>
+          <t>YFR033C</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>YLL009C</t>
+          <t>YKL150W</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>YBL059C-A</t>
+          <t>YCR079W</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>YFR033C</t>
+          <t>YDR353W</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>YAL039C</t>
+          <t>YKR071C</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>YLR038C</t>
+          <t>YGR181W</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>YLR193C</t>
+          <t>YLR043C</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>YNL036W</t>
+          <t>YEL039C</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>YCL057W</t>
+          <t>YLR218C</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>YDR353W</t>
+          <t>YDR511W</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>YDR511W</t>
+          <t>YKL195W</t>
         </is>
       </c>
     </row>
@@ -681,7 +681,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>YMR002W</t>
+          <t>YBL059C-A</t>
         </is>
       </c>
     </row>
@@ -691,7 +691,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>YKL195W</t>
+          <t>YMR228W</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>YOR090C</t>
+          <t>YPL132W</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>YMR194C-B</t>
+          <t>YKL053C-A</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>YDR031W</t>
+          <t>YCL057W</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>YNR020C</t>
+          <t>YJR048W</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>YMR244C-A</t>
+          <t>YMR194C-B</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>YML054C</t>
+          <t>YMR244C-A</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>YJR104C</t>
+          <t>YJR135W-A</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>YKL152C</t>
+          <t>YDR185C</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>YKR066C</t>
+          <t>YPR067W</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>YDR155C</t>
+          <t>YDR226W</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>YKL053C-A</t>
+          <t>YDR155C</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>YJL066C</t>
+          <t>YOR090C</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>YOR211C</t>
+          <t>YJR104C</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>YGR029W</t>
+          <t>YER057C</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>YIL160C</t>
+          <t>YLL018C-A</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>YER057C</t>
+          <t>YML050W</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>YJR048W</t>
+          <t>YNL036W</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>YML050W</t>
+          <t>YML054C</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>YBL107C</t>
+          <t>YKL084W</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>YPR067W</t>
+          <t>YNR020C</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>YBR035C</t>
+          <t>YDR031W</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>YKL067W</t>
+          <t>YGR029W</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>YLR168C</t>
+          <t>YAL039C</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>YDR487C</t>
+          <t>YBR056W</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>YJR034W</t>
+          <t>YKR066C</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>YDR430C</t>
+          <t>YLR168C</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>YJR135W-A</t>
+          <t>YIR037W</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>YMR228W</t>
+          <t>YOL143C</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>YLL018C-A</t>
+          <t>YBR035C</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>YKL084W</t>
+          <t>YLL009C</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>YKL087C</t>
+          <t>YIL160C</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>YOL143C</t>
+          <t>YDR430C</t>
         </is>
       </c>
     </row>
